--- a/script/qp_report.xlsx
+++ b/script/qp_report.xlsx
@@ -7,7 +7,7 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Data" sheetId="1" r:id="rId1"/>
+    <sheet name="Data and Charts" sheetId="1" r:id="rId1"/>
     <sheet name="Conclusion" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="124519"/>
@@ -205,7 +205,7 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Data!$A$2:$A$53</c:f>
+              <c:f>'Data and Charts'!$A$2:$A$53</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="52"/>
@@ -370,7 +370,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$B$2:$B$53</c:f>
+              <c:f>'Data and Charts'!$B$2:$B$53</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="52"/>
@@ -535,11 +535,11 @@
           </c:val>
         </c:ser>
         <c:marker val="1"/>
-        <c:axId val="113414144"/>
-        <c:axId val="113415680"/>
+        <c:axId val="122458112"/>
+        <c:axId val="122460416"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="113414144"/>
+        <c:axId val="122458112"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -565,14 +565,14 @@
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="113415680"/>
+        <c:crossAx val="122460416"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="113415680"/>
+        <c:axId val="122460416"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -598,7 +598,7 @@
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="113414144"/>
+        <c:crossAx val="122458112"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -611,7 +611,7 @@
   </c:chart>
   <c:printSettings>
     <c:headerFooter/>
-    <c:pageMargins b="0.75000000000000011" l="0.70000000000000007" r="0.70000000000000007" t="0.75000000000000011" header="0.30000000000000004" footer="0.30000000000000004"/>
+    <c:pageMargins b="0.75000000000000022" l="0.70000000000000018" r="0.70000000000000018" t="0.75000000000000022" header="0.3000000000000001" footer="0.3000000000000001"/>
     <c:pageSetup/>
   </c:printSettings>
 </c:chartSpace>
@@ -655,7 +655,7 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Data!$A$2:$A$53</c:f>
+              <c:f>'Data and Charts'!$A$2:$A$53</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="52"/>
@@ -820,7 +820,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$53</c:f>
+              <c:f>'Data and Charts'!$C$2:$C$53</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="52"/>
@@ -985,11 +985,11 @@
           </c:val>
         </c:ser>
         <c:marker val="1"/>
-        <c:axId val="113436160"/>
-        <c:axId val="113437696"/>
+        <c:axId val="122486144"/>
+        <c:axId val="122840576"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="113436160"/>
+        <c:axId val="122486144"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1009,14 +1009,14 @@
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="113437696"/>
+        <c:crossAx val="122840576"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="113437696"/>
+        <c:axId val="122840576"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1049,7 +1049,7 @@
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="113436160"/>
+        <c:crossAx val="122486144"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1062,7 +1062,7 @@
   </c:chart>
   <c:printSettings>
     <c:headerFooter/>
-    <c:pageMargins b="0.75000000000000011" l="0.70000000000000007" r="0.70000000000000007" t="0.75000000000000011" header="0.30000000000000004" footer="0.30000000000000004"/>
+    <c:pageMargins b="0.75000000000000022" l="0.70000000000000018" r="0.70000000000000018" t="0.75000000000000022" header="0.3000000000000001" footer="0.3000000000000001"/>
     <c:pageSetup/>
   </c:printSettings>
 </c:chartSpace>
@@ -1106,7 +1106,7 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Data!$A$2:$A$53</c:f>
+              <c:f>'Data and Charts'!$A$2:$A$53</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="52"/>
@@ -1271,7 +1271,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$D$2:$D$53</c:f>
+              <c:f>'Data and Charts'!$D$2:$D$53</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="52"/>
@@ -1436,11 +1436,11 @@
           </c:val>
         </c:ser>
         <c:marker val="1"/>
-        <c:axId val="113474176"/>
-        <c:axId val="113484160"/>
+        <c:axId val="122876288"/>
+        <c:axId val="122878208"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="113474176"/>
+        <c:axId val="122876288"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1466,14 +1466,14 @@
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="113484160"/>
+        <c:crossAx val="122878208"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="113484160"/>
+        <c:axId val="122878208"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1499,7 +1499,7 @@
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="113474176"/>
+        <c:crossAx val="122876288"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1512,7 +1512,7 @@
   </c:chart>
   <c:printSettings>
     <c:headerFooter/>
-    <c:pageMargins b="0.75000000000000011" l="0.70000000000000007" r="0.70000000000000007" t="0.75000000000000011" header="0.30000000000000004" footer="0.30000000000000004"/>
+    <c:pageMargins b="0.75000000000000022" l="0.70000000000000018" r="0.70000000000000018" t="0.75000000000000022" header="0.3000000000000001" footer="0.3000000000000001"/>
     <c:pageSetup/>
   </c:printSettings>
 </c:chartSpace>

--- a/script/qp_report.xlsx
+++ b/script/qp_report.xlsx
@@ -57,7 +57,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -74,14 +74,23 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="14"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="16"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -151,13 +160,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -535,11 +545,11 @@
           </c:val>
         </c:ser>
         <c:marker val="1"/>
-        <c:axId val="122458112"/>
-        <c:axId val="122460416"/>
+        <c:axId val="116887552"/>
+        <c:axId val="116889856"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="122458112"/>
+        <c:axId val="116887552"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -565,14 +575,14 @@
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="122460416"/>
+        <c:crossAx val="116889856"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="122460416"/>
+        <c:axId val="116889856"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -598,7 +608,7 @@
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="122458112"/>
+        <c:crossAx val="116887552"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -611,7 +621,7 @@
   </c:chart>
   <c:printSettings>
     <c:headerFooter/>
-    <c:pageMargins b="0.75000000000000022" l="0.70000000000000018" r="0.70000000000000018" t="0.75000000000000022" header="0.3000000000000001" footer="0.3000000000000001"/>
+    <c:pageMargins b="0.75000000000000033" l="0.70000000000000029" r="0.70000000000000029" t="0.75000000000000033" header="0.30000000000000016" footer="0.30000000000000016"/>
     <c:pageSetup/>
   </c:printSettings>
 </c:chartSpace>
@@ -985,11 +995,11 @@
           </c:val>
         </c:ser>
         <c:marker val="1"/>
-        <c:axId val="122486144"/>
-        <c:axId val="122840576"/>
+        <c:axId val="116915584"/>
+        <c:axId val="117335552"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="122486144"/>
+        <c:axId val="116915584"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1009,14 +1019,14 @@
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="122840576"/>
+        <c:crossAx val="117335552"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="122840576"/>
+        <c:axId val="117335552"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1049,7 +1059,7 @@
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="122486144"/>
+        <c:crossAx val="116915584"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1062,7 +1072,7 @@
   </c:chart>
   <c:printSettings>
     <c:headerFooter/>
-    <c:pageMargins b="0.75000000000000022" l="0.70000000000000018" r="0.70000000000000018" t="0.75000000000000022" header="0.3000000000000001" footer="0.3000000000000001"/>
+    <c:pageMargins b="0.75000000000000033" l="0.70000000000000029" r="0.70000000000000029" t="0.75000000000000033" header="0.30000000000000016" footer="0.30000000000000016"/>
     <c:pageSetup/>
   </c:printSettings>
 </c:chartSpace>
@@ -1436,11 +1446,11 @@
           </c:val>
         </c:ser>
         <c:marker val="1"/>
-        <c:axId val="122876288"/>
-        <c:axId val="122878208"/>
+        <c:axId val="117371264"/>
+        <c:axId val="117373184"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="122876288"/>
+        <c:axId val="117371264"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1466,14 +1476,14 @@
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="122878208"/>
+        <c:crossAx val="117373184"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="122878208"/>
+        <c:axId val="117373184"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1499,7 +1509,7 @@
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="122876288"/>
+        <c:crossAx val="117371264"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1512,7 +1522,7 @@
   </c:chart>
   <c:printSettings>
     <c:headerFooter/>
-    <c:pageMargins b="0.75000000000000022" l="0.70000000000000018" r="0.70000000000000018" t="0.75000000000000022" header="0.3000000000000001" footer="0.3000000000000001"/>
+    <c:pageMargins b="0.75000000000000033" l="0.70000000000000029" r="0.70000000000000029" t="0.75000000000000033" header="0.30000000000000016" footer="0.30000000000000016"/>
     <c:pageSetup/>
   </c:printSettings>
 </c:chartSpace>
@@ -1921,16 +1931,16 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="5">
+      <c r="A2" s="4">
         <v>0</v>
       </c>
-      <c r="B2" s="5">
+      <c r="B2" s="4">
         <v>15891</v>
       </c>
-      <c r="C2" s="5">
+      <c r="C2" s="4">
         <v>44.38</v>
       </c>
-      <c r="D2" s="5">
+      <c r="D2" s="4">
         <v>10848.26</v>
       </c>
     </row>
@@ -2657,50 +2667,58 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:A9"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="209.5703125" customWidth="1"/>
+    <col min="2" max="16384" width="9.140625" hidden="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="18.75">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:1" ht="21">
+      <c r="A1" s="6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:1" s="4" customFormat="1" ht="15.75">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:1" ht="21">
+      <c r="A2" s="5"/>
+    </row>
+    <row r="3" spans="1:1" s="3" customFormat="1" ht="15.75">
+      <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:1" s="4" customFormat="1" ht="15.75">
-      <c r="A3" s="4" t="s">
+    <row r="4" spans="1:1" s="3" customFormat="1" ht="15.75">
+      <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:1" s="4" customFormat="1" ht="15.75">
-      <c r="A4" s="4" t="s">
+    <row r="5" spans="1:1" s="3" customFormat="1" ht="15.75">
+      <c r="A5" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:1" s="4" customFormat="1" ht="15.75">
-      <c r="A5" s="4" t="s">
+    <row r="6" spans="1:1" s="3" customFormat="1" ht="15.75">
+      <c r="A6" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:1" s="4" customFormat="1" ht="15.75">
-      <c r="A6" s="4" t="s">
+    <row r="7" spans="1:1" s="3" customFormat="1" ht="15.75">
+      <c r="A7" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:1" s="4" customFormat="1" ht="15.75">
-      <c r="A7" s="4" t="s">
+    <row r="8" spans="1:1" s="3" customFormat="1" ht="15.75">
+      <c r="A8" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:1" s="4" customFormat="1" ht="15.75">
-      <c r="A8" s="4" t="s">
+    <row r="9" spans="1:1" s="3" customFormat="1" ht="15.75">
+      <c r="A9" s="3" t="s">
         <v>9</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>